--- a/data/hex_xlsx/OLVAS.HE.xlsx
+++ b/data/hex_xlsx/OLVAS.HE.xlsx
@@ -12162,13 +12162,34 @@
       <c r="P45" s="16">
         <v>1102.04</v>
       </c>
-      <c r="Q45" s="15"/>
-      <c r="R45" s="15"/>
-      <c r="S45" s="15"/>
-      <c r="T45" s="15"/>
-      <c r="U45" s="15"/>
-      <c r="V45" s="15"/>
-      <c r="W45" s="15"/>
+      <c r="Q45" s="24">
+        <f t="shared" ref="Q45:W45" si="1">SUM(Q43:Q44)</f>
+        <v>972.37</v>
+      </c>
+      <c r="R45" s="24">
+        <f t="shared" si="1"/>
+        <v>1038.96</v>
+      </c>
+      <c r="S45" s="24">
+        <f t="shared" si="1"/>
+        <v>1281.74</v>
+      </c>
+      <c r="T45" s="24">
+        <f t="shared" si="1"/>
+        <v>774.68</v>
+      </c>
+      <c r="U45" s="24">
+        <f t="shared" si="1"/>
+        <v>686.55</v>
+      </c>
+      <c r="V45" s="24">
+        <f t="shared" si="1"/>
+        <v>588.28</v>
+      </c>
+      <c r="W45" s="24">
+        <f t="shared" si="1"/>
+        <v>577.72</v>
+      </c>
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
